--- a/erp-server/erp-server-file/src/main/resources/excel/wms/sampleRecipient.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/sampleRecipient.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24945" windowHeight="17655"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,53 +29,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
-  <si>
-    <t>单据编号</t>
-  </si>
-  <si>
-    <t>要货类型</t>
-  </si>
-  <si>
-    <t>要货渠道</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+  <si>
+    <t>样品领用单号</t>
+  </si>
+  <si>
+    <t>领用日期</t>
+  </si>
+  <si>
+    <t>用途</t>
   </si>
   <si>
     <t>单据状态</t>
   </si>
   <si>
-    <t>拣货单生成</t>
-  </si>
-  <si>
-    <t>发货单生成</t>
-  </si>
-  <si>
-    <t>来源单号</t>
-  </si>
-  <si>
-    <t>货件单号</t>
-  </si>
-  <si>
-    <t>平台(第三方仓)SKU</t>
-  </si>
-  <si>
-    <t>平台产品ID</t>
-  </si>
-  <si>
-    <t>FNSKU</t>
-  </si>
-  <si>
-    <t>sku</t>
-  </si>
-  <si>
-    <t>样品领用单号</t>
-  </si>
-  <si>
-    <t>领用日期</t>
-  </si>
-  <si>
-    <t>用途</t>
-  </si>
-  <si>
     <t>作废状态</t>
   </si>
   <si>
@@ -121,52 +88,22 @@
     <t>{.code}</t>
   </si>
   <si>
-    <t>{.typeName}</t>
-  </si>
-  <si>
-    <t>{.channelName}</t>
-  </si>
-  <si>
-    <t>{.statusName}</t>
-  </si>
-  <si>
-    <t>{.pickPushDownStatusName}</t>
-  </si>
-  <si>
-    <t>{.deliveryPushDownStatusName}</t>
-  </si>
-  <si>
-    <t>{.sourceCode}</t>
-  </si>
-  <si>
-    <t>{.fbaShipmentCode}</t>
-  </si>
-  <si>
-    <t>{.thirdWarehouseSku}</t>
-  </si>
-  <si>
-    <t>{.platformProductId}</t>
-  </si>
-  <si>
-    <t>{.platformFnSku}</t>
+    <t>{.recipientDate}</t>
+  </si>
+  <si>
+    <t>{.usage}</t>
+  </si>
+  <si>
+    <t>{.approveStatusName}</t>
+  </si>
+  <si>
+    <t>{.invalidStatusName}</t>
+  </si>
+  <si>
+    <t>{.execStatusName}</t>
   </si>
   <si>
     <t>{.skuNo}</t>
-  </si>
-  <si>
-    <t>{.recipientDate}</t>
-  </si>
-  <si>
-    <t>{.usage}</t>
-  </si>
-  <si>
-    <t>{.approveStatusName}</t>
-  </si>
-  <si>
-    <t>{.invalidStatusName}</t>
-  </si>
-  <si>
-    <t>{.execStatusName}</t>
   </si>
   <si>
     <t>{.productName}</t>
@@ -212,7 +149,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,22 +176,6 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF4A4A4A"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF4A4A4A"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -739,137 +660,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -883,12 +804,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1242,40 +1157,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="16.125" customWidth="1"/>
-    <col min="2" max="2" width="8.5" customWidth="1"/>
-    <col min="3" max="3" width="27.375" customWidth="1"/>
-    <col min="4" max="4" width="8.125" customWidth="1"/>
-    <col min="5" max="5" width="26.625" customWidth="1"/>
-    <col min="6" max="6" width="32.25" customWidth="1"/>
-    <col min="7" max="8" width="20.75" customWidth="1"/>
-    <col min="9" max="9" width="20.625" customWidth="1"/>
-    <col min="10" max="11" width="13.875" customWidth="1"/>
-    <col min="12" max="12" width="12.625" customWidth="1"/>
-    <col min="13" max="13" width="42" customWidth="1"/>
-    <col min="14" max="14" width="14.375" customWidth="1"/>
-    <col min="15" max="15" width="13.125" customWidth="1"/>
-    <col min="16" max="16" width="10.25" customWidth="1"/>
-    <col min="17" max="17" width="26.75" customWidth="1"/>
-    <col min="18" max="19" width="27.375" customWidth="1"/>
-    <col min="20" max="20" width="28" customWidth="1"/>
-    <col min="21" max="21" width="16.375" customWidth="1"/>
-    <col min="22" max="22" width="21.25" customWidth="1"/>
-    <col min="23" max="23" width="10.625" customWidth="1"/>
-    <col min="24" max="24" width="22.25" customWidth="1"/>
-    <col min="25" max="25" width="19.25" customWidth="1"/>
-    <col min="26" max="26" width="17.25" customWidth="1"/>
-    <col min="27" max="27" width="20" customWidth="1"/>
-    <col min="28" max="28" width="17.25" customWidth="1"/>
-    <col min="29" max="29" width="16" customWidth="1"/>
-    <col min="30" max="30" width="9.375" customWidth="1"/>
-    <col min="31" max="31" width="14.375" customWidth="1"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="14.375" customWidth="1"/>
+    <col min="3" max="3" width="13.125" customWidth="1"/>
+    <col min="4" max="4" width="10.25" customWidth="1"/>
+    <col min="5" max="5" width="26.75" customWidth="1"/>
+    <col min="6" max="7" width="27.375" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="9" max="9" width="16.375" customWidth="1"/>
+    <col min="10" max="10" width="21.25" customWidth="1"/>
+    <col min="11" max="11" width="10.625" customWidth="1"/>
+    <col min="12" max="12" width="22.25" customWidth="1"/>
+    <col min="13" max="13" width="19.25" customWidth="1"/>
+    <col min="14" max="14" width="17.25" customWidth="1"/>
+    <col min="15" max="15" width="20" customWidth="1"/>
+    <col min="16" max="16" width="17.25" customWidth="1"/>
+    <col min="17" max="17" width="16" customWidth="1"/>
+    <col min="18" max="18" width="9.375" customWidth="1"/>
+    <col min="19" max="19" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:30">
+    <row r="1" s="1" customFormat="1" spans="1:18">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1300,163 +1205,91 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q1" s="3" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="3" t="s">
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:18">
+      <c r="A2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="F2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="7" t="s">
+      <c r="G2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="H2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="7" t="s">
+      <c r="I2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="7" t="s">
+      <c r="J2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="7" t="s">
+      <c r="K2" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:30">
-      <c r="A2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="M2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="N2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="O2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="P2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="Q2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="R2" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/sampleRecipient.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/sampleRecipient.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>样品领用单号</t>
   </si>
@@ -40,6 +40,15 @@
     <t>用途</t>
   </si>
   <si>
+    <t>是否需要出库</t>
+  </si>
+  <si>
+    <t>不出库原因</t>
+  </si>
+  <si>
+    <t>是否需要入台账</t>
+  </si>
+  <si>
     <t>单据状态</t>
   </si>
   <si>
@@ -92,6 +101,15 @@
   </si>
   <si>
     <t>{.usage}</t>
+  </si>
+  <si>
+    <t>{.isOutstockRequiredName}</t>
+  </si>
+  <si>
+    <t>{.noOutstockReason}</t>
+  </si>
+  <si>
+    <t>{.isLedgerRequiredName}</t>
   </si>
   <si>
     <t>{.approveStatusName}</t>
@@ -1157,30 +1175,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="14.375" customWidth="1"/>
     <col min="3" max="3" width="13.125" customWidth="1"/>
-    <col min="4" max="4" width="10.25" customWidth="1"/>
-    <col min="5" max="5" width="26.75" customWidth="1"/>
-    <col min="6" max="7" width="27.375" customWidth="1"/>
-    <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="16.375" customWidth="1"/>
-    <col min="10" max="10" width="21.25" customWidth="1"/>
-    <col min="11" max="11" width="10.625" customWidth="1"/>
-    <col min="12" max="12" width="22.25" customWidth="1"/>
-    <col min="13" max="13" width="19.25" customWidth="1"/>
-    <col min="14" max="14" width="17.25" customWidth="1"/>
-    <col min="15" max="15" width="20" customWidth="1"/>
-    <col min="16" max="16" width="17.25" customWidth="1"/>
-    <col min="17" max="17" width="16" customWidth="1"/>
-    <col min="18" max="18" width="9.375" customWidth="1"/>
-    <col min="19" max="19" width="14.375" customWidth="1"/>
+    <col min="4" max="7" width="10.25" customWidth="1"/>
+    <col min="8" max="8" width="26.75" customWidth="1"/>
+    <col min="9" max="10" width="27.375" customWidth="1"/>
+    <col min="11" max="11" width="28" customWidth="1"/>
+    <col min="12" max="12" width="16.375" customWidth="1"/>
+    <col min="13" max="13" width="21.25" customWidth="1"/>
+    <col min="14" max="14" width="10.625" customWidth="1"/>
+    <col min="15" max="15" width="22.25" customWidth="1"/>
+    <col min="16" max="16" width="19.25" customWidth="1"/>
+    <col min="17" max="17" width="17.25" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
+    <col min="19" max="19" width="17.25" customWidth="1"/>
+    <col min="20" max="20" width="16" customWidth="1"/>
+    <col min="21" max="21" width="9.375" customWidth="1"/>
+    <col min="22" max="22" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:18">
+    <row r="1" s="1" customFormat="1" spans="1:21">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1217,13 +1235,13 @@
       <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="5" t="s">
@@ -1235,61 +1253,79 @@
       <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:18">
+    <row r="2" s="2" customFormat="1" spans="1:21">
       <c r="A2" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O2" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="M2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="P2" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/sampleRecipient.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/sampleRecipient.xlsx
@@ -46,36 +46,36 @@
     <t>不出库原因</t>
   </si>
   <si>
+    <t>单据状态</t>
+  </si>
+  <si>
+    <t>作废状态</t>
+  </si>
+  <si>
+    <t>执行状态</t>
+  </si>
+  <si>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>产品名称</t>
+  </si>
+  <si>
+    <t>发货仓库</t>
+  </si>
+  <si>
+    <t>领用数量</t>
+  </si>
+  <si>
+    <t>待出库数量</t>
+  </si>
+  <si>
+    <t>已出库数量</t>
+  </si>
+  <si>
     <t>是否需要入台账</t>
   </si>
   <si>
-    <t>单据状态</t>
-  </si>
-  <si>
-    <t>作废状态</t>
-  </si>
-  <si>
-    <t>执行状态</t>
-  </si>
-  <si>
-    <t>SKU</t>
-  </si>
-  <si>
-    <t>产品名称</t>
-  </si>
-  <si>
-    <t>发货仓库</t>
-  </si>
-  <si>
-    <t>领用数量</t>
-  </si>
-  <si>
-    <t>待出库数量</t>
-  </si>
-  <si>
-    <t>已出库数量</t>
-  </si>
-  <si>
     <t>备注</t>
   </si>
   <si>
@@ -109,34 +109,34 @@
     <t>{.noOutstockReason}</t>
   </si>
   <si>
+    <t>{.approveStatusName}</t>
+  </si>
+  <si>
+    <t>{.invalidStatusName}</t>
+  </si>
+  <si>
+    <t>{.execStatusName}</t>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.productName}</t>
+  </si>
+  <si>
+    <t>{.warehouseName}</t>
+  </si>
+  <si>
+    <t>{.recipientQty}</t>
+  </si>
+  <si>
+    <t>{.reservedQty}</t>
+  </si>
+  <si>
+    <t>{.deliveryQty}</t>
+  </si>
+  <si>
     <t>{.isLedgerRequiredName}</t>
-  </si>
-  <si>
-    <t>{.approveStatusName}</t>
-  </si>
-  <si>
-    <t>{.invalidStatusName}</t>
-  </si>
-  <si>
-    <t>{.execStatusName}</t>
-  </si>
-  <si>
-    <t>{.skuNo}</t>
-  </si>
-  <si>
-    <t>{.productName}</t>
-  </si>
-  <si>
-    <t>{.warehouseName}</t>
-  </si>
-  <si>
-    <t>{.recipientQty}</t>
-  </si>
-  <si>
-    <t>{.reservedQty}</t>
-  </si>
-  <si>
-    <t>{.deliveryQty}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -1181,14 +1181,15 @@
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="14.375" customWidth="1"/>
     <col min="3" max="3" width="13.125" customWidth="1"/>
-    <col min="4" max="7" width="10.25" customWidth="1"/>
-    <col min="8" max="8" width="26.75" customWidth="1"/>
-    <col min="9" max="10" width="27.375" customWidth="1"/>
-    <col min="11" max="11" width="28" customWidth="1"/>
-    <col min="12" max="12" width="16.375" customWidth="1"/>
-    <col min="13" max="13" width="21.25" customWidth="1"/>
-    <col min="14" max="14" width="10.625" customWidth="1"/>
-    <col min="15" max="15" width="22.25" customWidth="1"/>
+    <col min="4" max="6" width="10.25" customWidth="1"/>
+    <col min="7" max="7" width="26.75" customWidth="1"/>
+    <col min="8" max="9" width="27.375" customWidth="1"/>
+    <col min="10" max="10" width="28" customWidth="1"/>
+    <col min="11" max="11" width="16.375" customWidth="1"/>
+    <col min="12" max="12" width="21.25" customWidth="1"/>
+    <col min="13" max="13" width="10.625" customWidth="1"/>
+    <col min="14" max="14" width="22.25" customWidth="1"/>
+    <col min="15" max="15" width="10.25" customWidth="1"/>
     <col min="16" max="16" width="19.25" customWidth="1"/>
     <col min="17" max="17" width="17.25" customWidth="1"/>
     <col min="18" max="18" width="20" customWidth="1"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/sampleRecipient.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/sampleRecipient.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>样品领用单号</t>
   </si>
@@ -64,6 +64,9 @@
     <t>发货仓库</t>
   </si>
   <si>
+    <t>仓库负责人</t>
+  </si>
+  <si>
     <t>领用数量</t>
   </si>
   <si>
@@ -125,6 +128,9 @@
   </si>
   <si>
     <t>{.warehouseName}</t>
+  </si>
+  <si>
+    <t>{.warehouseChargeName}</t>
   </si>
   <si>
     <t>{.recipientQty}</t>
@@ -1175,7 +1181,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -1186,20 +1192,20 @@
     <col min="8" max="9" width="27.375" customWidth="1"/>
     <col min="10" max="10" width="28" customWidth="1"/>
     <col min="11" max="11" width="16.375" customWidth="1"/>
-    <col min="12" max="12" width="21.25" customWidth="1"/>
-    <col min="13" max="13" width="10.625" customWidth="1"/>
-    <col min="14" max="14" width="22.25" customWidth="1"/>
-    <col min="15" max="15" width="10.25" customWidth="1"/>
-    <col min="16" max="16" width="19.25" customWidth="1"/>
-    <col min="17" max="17" width="17.25" customWidth="1"/>
-    <col min="18" max="18" width="20" customWidth="1"/>
-    <col min="19" max="19" width="17.25" customWidth="1"/>
-    <col min="20" max="20" width="16" customWidth="1"/>
-    <col min="21" max="21" width="9.375" customWidth="1"/>
-    <col min="22" max="22" width="14.375" customWidth="1"/>
+    <col min="12" max="13" width="21.25" customWidth="1"/>
+    <col min="14" max="14" width="10.625" customWidth="1"/>
+    <col min="15" max="15" width="22.25" customWidth="1"/>
+    <col min="16" max="16" width="10.25" customWidth="1"/>
+    <col min="17" max="17" width="19.25" customWidth="1"/>
+    <col min="18" max="18" width="17.25" customWidth="1"/>
+    <col min="19" max="19" width="20" customWidth="1"/>
+    <col min="20" max="20" width="17.25" customWidth="1"/>
+    <col min="21" max="21" width="16" customWidth="1"/>
+    <col min="22" max="22" width="9.375" customWidth="1"/>
+    <col min="23" max="23" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:21">
+    <row r="1" s="1" customFormat="1" spans="1:22">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1245,7 +1251,7 @@
       <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="5" t="s">
@@ -1263,70 +1269,76 @@
       <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="5" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:21">
+    <row r="2" s="2" customFormat="1" spans="1:22">
       <c r="A2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="P2" s="2" t="s">
         <v>36</v>
       </c>
+      <c r="P2" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="Q2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/sampleRecipient.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/sampleRecipient.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>样品领用单号</t>
   </si>
@@ -40,6 +40,9 @@
     <t>用途</t>
   </si>
   <si>
+    <t>用途说明</t>
+  </si>
+  <si>
     <t>是否需要出库</t>
   </si>
   <si>
@@ -104,6 +107,9 @@
   </si>
   <si>
     <t>{.usage}</t>
+  </si>
+  <si>
+    <t>{.usageDesc}</t>
   </si>
   <si>
     <t>{.isOutstockRequiredName}</t>
@@ -827,10 +833,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1181,31 +1187,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="14.375" customWidth="1"/>
     <col min="3" max="3" width="13.125" customWidth="1"/>
-    <col min="4" max="6" width="10.25" customWidth="1"/>
-    <col min="7" max="7" width="26.75" customWidth="1"/>
-    <col min="8" max="9" width="27.375" customWidth="1"/>
-    <col min="10" max="10" width="28" customWidth="1"/>
-    <col min="11" max="11" width="16.375" customWidth="1"/>
-    <col min="12" max="13" width="21.25" customWidth="1"/>
-    <col min="14" max="14" width="10.625" customWidth="1"/>
-    <col min="15" max="15" width="22.25" customWidth="1"/>
-    <col min="16" max="16" width="10.25" customWidth="1"/>
-    <col min="17" max="17" width="19.25" customWidth="1"/>
-    <col min="18" max="18" width="17.25" customWidth="1"/>
-    <col min="19" max="19" width="20" customWidth="1"/>
-    <col min="20" max="20" width="17.25" customWidth="1"/>
-    <col min="21" max="21" width="16" customWidth="1"/>
-    <col min="22" max="22" width="9.375" customWidth="1"/>
-    <col min="23" max="23" width="14.375" customWidth="1"/>
+    <col min="4" max="4" width="12.125" customWidth="1"/>
+    <col min="5" max="7" width="10.25" customWidth="1"/>
+    <col min="8" max="8" width="26.75" customWidth="1"/>
+    <col min="9" max="10" width="27.375" customWidth="1"/>
+    <col min="11" max="11" width="28" customWidth="1"/>
+    <col min="12" max="12" width="16.375" customWidth="1"/>
+    <col min="13" max="14" width="21.25" customWidth="1"/>
+    <col min="15" max="15" width="10.625" customWidth="1"/>
+    <col min="16" max="16" width="22.25" customWidth="1"/>
+    <col min="17" max="17" width="10.25" customWidth="1"/>
+    <col min="18" max="18" width="19.25" customWidth="1"/>
+    <col min="19" max="19" width="17.25" customWidth="1"/>
+    <col min="20" max="20" width="20" customWidth="1"/>
+    <col min="21" max="21" width="17.25" customWidth="1"/>
+    <col min="22" max="22" width="16" customWidth="1"/>
+    <col min="23" max="23" width="9.375" customWidth="1"/>
+    <col min="24" max="24" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:22">
+    <row r="1" s="1" customFormat="1" spans="1:23">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1254,91 +1261,97 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="W1" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:22">
-      <c r="A2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="2" s="2" customFormat="1" spans="1:23">
+      <c r="A2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="J2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="K2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="L2" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="M2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="N2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="O2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="P2" s="5" t="s">
         <v>38</v>
       </c>
+      <c r="Q2" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="R2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/sampleRecipient.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/sampleRecipient.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>样品领用单号</t>
   </si>
@@ -55,6 +55,9 @@
     <t>作废状态</t>
   </si>
   <si>
+    <t>跟踪号</t>
+  </si>
+  <si>
     <t>执行状态</t>
   </si>
   <si>
@@ -122,6 +125,9 @@
   </si>
   <si>
     <t>{.invalidStatusName}</t>
+  </si>
+  <si>
+    <t>{.trackNo}</t>
   </si>
   <si>
     <t>{.execStatusName}</t>
@@ -1187,7 +1193,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -1196,23 +1202,23 @@
     <col min="4" max="4" width="12.125" customWidth="1"/>
     <col min="5" max="7" width="10.25" customWidth="1"/>
     <col min="8" max="8" width="26.75" customWidth="1"/>
-    <col min="9" max="10" width="27.375" customWidth="1"/>
-    <col min="11" max="11" width="28" customWidth="1"/>
-    <col min="12" max="12" width="16.375" customWidth="1"/>
-    <col min="13" max="14" width="21.25" customWidth="1"/>
-    <col min="15" max="15" width="10.625" customWidth="1"/>
-    <col min="16" max="16" width="22.25" customWidth="1"/>
-    <col min="17" max="17" width="10.25" customWidth="1"/>
-    <col min="18" max="18" width="19.25" customWidth="1"/>
-    <col min="19" max="19" width="17.25" customWidth="1"/>
-    <col min="20" max="20" width="20" customWidth="1"/>
-    <col min="21" max="21" width="17.25" customWidth="1"/>
-    <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="23" width="9.375" customWidth="1"/>
-    <col min="24" max="24" width="14.375" customWidth="1"/>
+    <col min="9" max="11" width="27.375" customWidth="1"/>
+    <col min="12" max="12" width="28" customWidth="1"/>
+    <col min="13" max="13" width="16.375" customWidth="1"/>
+    <col min="14" max="15" width="21.25" customWidth="1"/>
+    <col min="16" max="16" width="10.625" customWidth="1"/>
+    <col min="17" max="17" width="22.25" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
+    <col min="19" max="19" width="19.25" customWidth="1"/>
+    <col min="20" max="20" width="17.25" customWidth="1"/>
+    <col min="21" max="21" width="20" customWidth="1"/>
+    <col min="22" max="22" width="17.25" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
+    <col min="24" max="24" width="9.375" customWidth="1"/>
+    <col min="25" max="25" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:23">
+    <row r="1" s="1" customFormat="1" spans="1:24">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1264,7 +1270,7 @@
       <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="4" t="s">
@@ -1282,76 +1288,82 @@
       <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:23">
+    <row r="2" s="2" customFormat="1" spans="1:24">
       <c r="A2" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="R2" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="R2" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="S2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/sampleRecipient.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/sampleRecipient.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>样品领用单号</t>
   </si>
@@ -97,6 +97,12 @@
     <t>领用人</t>
   </si>
   <si>
+    <t>领用部门</t>
+  </si>
+  <si>
+    <t>领料组织</t>
+  </si>
+  <si>
     <t>创建人</t>
   </si>
   <si>
@@ -167,6 +173,12 @@
   </si>
   <si>
     <t>{.userName}</t>
+  </si>
+  <si>
+    <t>{.deptName}</t>
+  </si>
+  <si>
+    <t>{.pickOrgName}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -1193,7 +1205,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -1212,13 +1224,13 @@
     <col min="19" max="19" width="19.25" customWidth="1"/>
     <col min="20" max="20" width="17.25" customWidth="1"/>
     <col min="21" max="21" width="20" customWidth="1"/>
-    <col min="22" max="22" width="17.25" customWidth="1"/>
-    <col min="23" max="23" width="16" customWidth="1"/>
-    <col min="24" max="24" width="9.375" customWidth="1"/>
-    <col min="25" max="25" width="14.375" customWidth="1"/>
+    <col min="22" max="24" width="17.25" customWidth="1"/>
+    <col min="25" max="25" width="16" customWidth="1"/>
+    <col min="26" max="26" width="9.375" customWidth="1"/>
+    <col min="27" max="27" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:24">
+    <row r="1" s="1" customFormat="1" spans="1:26">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1291,79 +1303,91 @@
       <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:24">
+    <row r="2" s="2" customFormat="1" spans="1:26">
       <c r="A2" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
